--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ82"/>
+  <dimension ref="A1:AZ83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115377556</v>
+        <v>136646193</v>
       </c>
       <c r="B10" t="n">
-        <v>4775</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,32 +1622,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1655,13 +1658,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517017</v>
+        <v>516931</v>
       </c>
       <c r="R10" t="n">
-        <v>6540497</v>
+        <v>6540289</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,22 +1688,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>20:15, i SV, landar 50 m bort, rapar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,31 +1717,30 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Amanda Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377556</t>
+          <t>https://artportalen.se/Sighting/136646193</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115377695</v>
+        <v>115377556</v>
       </c>
       <c r="B11" t="n">
         <v>4775</v>
@@ -1777,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517002</v>
+        <v>517017</v>
       </c>
       <c r="R11" t="n">
-        <v>6540481</v>
+        <v>6540497</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,16 +1856,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377695</t>
+          <t>https://artportalen.se/Sighting/115377556</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115377558</v>
+        <v>115377695</v>
       </c>
       <c r="B12" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1866,21 +1873,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517017</v>
+        <v>517002</v>
       </c>
       <c r="R12" t="n">
-        <v>6540497</v>
+        <v>6540481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1971,16 +1978,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377558</t>
+          <t>https://artportalen.se/Sighting/115377695</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129810216</v>
+        <v>115377558</v>
       </c>
       <c r="B13" t="n">
-        <v>97983</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1988,45 +1995,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vedkärret, Nrk</t>
+          <t>Skepphultamossen, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521391</v>
+        <v>517017</v>
       </c>
       <c r="R13" t="n">
-        <v>6539013</v>
+        <v>6540497</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2050,17 +2058,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2086,22 +2094,22 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810216</t>
+          <t>https://artportalen.se/Sighting/115377558</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133708635</v>
+        <v>129810216</v>
       </c>
       <c r="B14" t="n">
-        <v>58308</v>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,43 +2117,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103008</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rösjön, Rösjön, Nrk</t>
+          <t>Vedkärret, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>516741</v>
+        <v>521391</v>
       </c>
       <c r="R14" t="n">
-        <v>6539120</v>
+        <v>6539013</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2172,22 +2179,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,33 +2203,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133708635</t>
+          <t>https://artportalen.se/Sighting/129810216</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134855725</v>
+        <v>133708635</v>
       </c>
       <c r="B15" t="n">
-        <v>99210</v>
+        <v>58308</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,51 +2238,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>103008</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stakgölsmossen, Nrk</t>
+          <t>Rösjön, Rösjön, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516726</v>
+        <v>516741</v>
       </c>
       <c r="R15" t="n">
-        <v>6538929</v>
+        <v>6539120</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2298,12 +2301,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,27 +2331,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134855725</t>
+          <t>https://artportalen.se/Sighting/133708635</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97155205</v>
+        <v>134855725</v>
       </c>
       <c r="B16" t="n">
-        <v>97983</v>
+        <v>99210</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2346,41 +2359,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516810</v>
+        <v>516726</v>
       </c>
       <c r="R16" t="n">
-        <v>6538951</v>
+        <v>6538929</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,17 +2427,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,34 +2441,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97155205</t>
+          <t>https://artportalen.se/Sighting/134855725</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108401900</v>
+        <v>97155205</v>
       </c>
       <c r="B17" t="n">
-        <v>96708</v>
+        <v>97983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2458,45 +2475,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tärnmossemon, Nrk</t>
+          <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520654</v>
+        <v>516810</v>
       </c>
       <c r="R17" t="n">
-        <v>6538974</v>
+        <v>6538951</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2520,22 +2533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,16 +2570,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108401900</t>
+          <t>https://artportalen.se/Sighting/97155205</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>62126985</v>
+        <v>108401900</v>
       </c>
       <c r="B18" t="n">
-        <v>97986</v>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,37 +2587,45 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skåle 0850/5550, Nrk</t>
+          <t>Tärnmossemon, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511839</v>
+        <v>520654</v>
       </c>
       <c r="R18" t="n">
-        <v>6538728</v>
+        <v>6538974</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2628,22 +2644,27 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,33 +2673,34 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62126985</t>
+          <t>https://artportalen.se/Sighting/108401900</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98669244</v>
+        <v>62126985</v>
       </c>
       <c r="B19" t="n">
-        <v>96554</v>
+        <v>97986</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,49 +2708,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>210</v>
+        <v>221946</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gropadalen, Nrk</t>
+          <t>Skåle 0850/5550, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509662</v>
+        <v>511839</v>
       </c>
       <c r="R19" t="n">
-        <v>6538673</v>
+        <v>6538728</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2752,12 +2762,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>1984-12-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>1984-12-12</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,81 +2781,80 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98669244</t>
+          <t>https://artportalen.se/Sighting/62126985</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135018500</v>
+        <v>98669244</v>
       </c>
       <c r="B20" t="n">
-        <v>58141</v>
+        <v>96554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hovdesjön. bäcken, Nrk</t>
+          <t>Gropadalen, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>512422</v>
+        <v>509662</v>
       </c>
       <c r="R20" t="n">
-        <v>6538962</v>
+        <v>6538673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2867,22 +2881,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,60 +2895,61 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135018500</t>
+          <t>https://artportalen.se/Sighting/98669244</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135018493</v>
+        <v>135018500</v>
       </c>
       <c r="B21" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -3032,16 +3037,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135018493</t>
+          <t>https://artportalen.se/Sighting/135018500</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129810221</v>
+        <v>135018493</v>
       </c>
       <c r="B22" t="n">
-        <v>97394</v>
+        <v>58136</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3049,45 +3054,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>103023</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Aggsjön, Nrk</t>
+          <t>Hovdesjön. bäcken, Nrk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521076</v>
+        <v>512422</v>
       </c>
       <c r="R22" t="n">
-        <v>6538419</v>
+        <v>6538962</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3106,12 +3115,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3121,12 +3130,12 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,66 +3144,65 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810221</t>
+          <t>https://artportalen.se/Sighting/135018493</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129810223</v>
+        <v>129810221</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>97394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3202,10 +3210,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521077</v>
+        <v>521076</v>
       </c>
       <c r="R23" t="n">
-        <v>6538398</v>
+        <v>6538419</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3250,17 +3258,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3278,47 +3282,46 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810223</t>
+          <t>https://artportalen.se/Sighting/129810221</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129810219</v>
+        <v>129810223</v>
       </c>
       <c r="B24" t="n">
-        <v>4775</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3328,10 +3331,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521090</v>
+        <v>521077</v>
       </c>
       <c r="R24" t="n">
-        <v>6538419</v>
+        <v>6538398</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3376,13 +3379,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3400,16 +3407,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810219</t>
+          <t>https://artportalen.se/Sighting/129810223</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129810218</v>
+        <v>129810219</v>
       </c>
       <c r="B25" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3417,21 +3424,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3522,16 +3529,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810218</t>
+          <t>https://artportalen.se/Sighting/129810219</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129810217</v>
+        <v>129810218</v>
       </c>
       <c r="B26" t="n">
-        <v>97983</v>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3539,31 +3546,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3571,10 +3579,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521141</v>
+        <v>521090</v>
       </c>
       <c r="R26" t="n">
-        <v>6538398</v>
+        <v>6538419</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3643,33 +3651,33 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810217</t>
+          <t>https://artportalen.se/Sighting/129810218</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67277679</v>
+        <v>129810217</v>
       </c>
       <c r="B27" t="n">
-        <v>109866</v>
+        <v>97983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220228</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3677,35 +3685,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kållslätt, 525 m NNO om, Nrk</t>
+          <t>Aggsjön, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510443</v>
+        <v>521141</v>
       </c>
       <c r="R27" t="n">
-        <v>6538515</v>
+        <v>6538398</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3724,22 +3725,27 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Hal-0031</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3748,42 +3754,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Skogsvägkant</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67277679</t>
+          <t>https://artportalen.se/Sighting/129810217</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128760477</v>
+        <v>67277679</v>
       </c>
       <c r="B28" t="n">
-        <v>93197</v>
+        <v>109866</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3791,44 +3789,52 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220228</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gruvemon, Nrk</t>
+          <t>Kållslätt, 525 m NNO om, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517886</v>
+        <v>510443</v>
       </c>
       <c r="R28" t="n">
-        <v>6536773</v>
+        <v>6538515</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3847,27 +3853,22 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Hal-0031</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3876,34 +3877,42 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Skogsvägkant</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760477</t>
+          <t>https://artportalen.se/Sighting/67277679</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120432305</v>
+        <v>128760477</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>93197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,44 +3920,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
+          <t>Gruvemon, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518189</v>
+        <v>517886</v>
       </c>
       <c r="R29" t="n">
-        <v>6536658</v>
+        <v>6536773</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3972,22 +3981,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4014,16 +4023,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432305</t>
+          <t>https://artportalen.se/Sighting/128760477</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120432283</v>
+        <v>120432305</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4031,21 +4040,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4134,13 +4143,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432283</t>
+          <t>https://artportalen.se/Sighting/120432305</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120432395</v>
+        <v>120432283</v>
       </c>
       <c r="B31" t="n">
         <v>79946</v>
@@ -4178,14 +4187,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fåglamossen, Nrk</t>
+          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518363</v>
+        <v>518189</v>
       </c>
       <c r="R31" t="n">
-        <v>6536679</v>
+        <v>6536658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4254,59 +4263,58 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432395</t>
+          <t>https://artportalen.se/Sighting/120432283</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115463834</v>
+        <v>120432395</v>
       </c>
       <c r="B32" t="n">
-        <v>97394</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ommekärrsmossen, Nrk</t>
+          <t>Fåglamossen, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521356</v>
+        <v>518363</v>
       </c>
       <c r="R32" t="n">
-        <v>6536843</v>
+        <v>6536679</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4333,22 +4341,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4375,13 +4383,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463834</t>
+          <t>https://artportalen.se/Sighting/120432395</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115464064</v>
+        <v>115463834</v>
       </c>
       <c r="B33" t="n">
         <v>97394</v>
@@ -4424,10 +4432,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521284</v>
+        <v>521356</v>
       </c>
       <c r="R33" t="n">
-        <v>6536870</v>
+        <v>6536843</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4496,16 +4504,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115464064</t>
+          <t>https://artportalen.se/Sighting/115463834</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115463863</v>
+        <v>115464064</v>
       </c>
       <c r="B34" t="n">
-        <v>92333</v>
+        <v>97394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4513,30 +4521,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4217</v>
+        <v>2590</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4544,10 +4553,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521375</v>
+        <v>521284</v>
       </c>
       <c r="R34" t="n">
-        <v>6536833</v>
+        <v>6536870</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4616,16 +4625,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463863</t>
+          <t>https://artportalen.se/Sighting/115464064</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115463816</v>
+        <v>115463863</v>
       </c>
       <c r="B35" t="n">
-        <v>5179</v>
+        <v>92333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4633,32 +4642,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>4217</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4666,10 +4673,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521348</v>
+        <v>521375</v>
       </c>
       <c r="R35" t="n">
-        <v>6536870</v>
+        <v>6536833</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4738,16 +4745,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463816</t>
+          <t>https://artportalen.se/Sighting/115463863</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120635109</v>
+        <v>115463816</v>
       </c>
       <c r="B36" t="n">
-        <v>97394</v>
+        <v>5179</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4755,42 +4762,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Ommekärrsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517608</v>
+        <v>521348</v>
       </c>
       <c r="R36" t="n">
-        <v>6536616</v>
+        <v>6536870</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4817,22 +4825,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4859,16 +4867,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635109</t>
+          <t>https://artportalen.se/Sighting/115463816</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120635189</v>
+        <v>120635109</v>
       </c>
       <c r="B37" t="n">
-        <v>91872</v>
+        <v>97394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4876,41 +4884,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517634</v>
+        <v>517608</v>
       </c>
       <c r="R37" t="n">
-        <v>6536147</v>
+        <v>6536616</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4979,44 +4988,44 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635189</t>
+          <t>https://artportalen.se/Sighting/120635109</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120635175</v>
+        <v>120635189</v>
       </c>
       <c r="B38" t="n">
-        <v>93235</v>
+        <v>91872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5027,10 +5036,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>517662</v>
+        <v>517634</v>
       </c>
       <c r="R38" t="n">
-        <v>6536294</v>
+        <v>6536147</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5099,16 +5108,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635175</t>
+          <t>https://artportalen.se/Sighting/120635189</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120635132</v>
+        <v>120635175</v>
       </c>
       <c r="B39" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5116,41 +5125,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>517612</v>
+        <v>517662</v>
       </c>
       <c r="R39" t="n">
-        <v>6536339</v>
+        <v>6536294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5219,16 +5228,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635132</t>
+          <t>https://artportalen.se/Sighting/120635175</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120635182</v>
+        <v>120635132</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>75428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5236,21 +5245,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5263,14 +5272,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>517625</v>
+        <v>517612</v>
       </c>
       <c r="R40" t="n">
-        <v>6536200</v>
+        <v>6536339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5339,16 +5348,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635182</t>
+          <t>https://artportalen.se/Sighting/120635132</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120635185</v>
+        <v>120635182</v>
       </c>
       <c r="B41" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5356,21 +5365,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5387,10 +5396,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517623</v>
+        <v>517625</v>
       </c>
       <c r="R41" t="n">
-        <v>6536181</v>
+        <v>6536200</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5459,49 +5468,47 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635185</t>
+          <t>https://artportalen.se/Sighting/120635182</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120635120</v>
+        <v>120635185</v>
       </c>
       <c r="B42" t="n">
-        <v>4775</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5509,10 +5516,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>517619</v>
+        <v>517623</v>
       </c>
       <c r="R42" t="n">
-        <v>6536384</v>
+        <v>6536181</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5581,16 +5588,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635120</t>
+          <t>https://artportalen.se/Sighting/120635185</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120635095</v>
+        <v>120635120</v>
       </c>
       <c r="B43" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5598,21 +5605,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5627,14 +5634,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>517618</v>
+        <v>517619</v>
       </c>
       <c r="R43" t="n">
-        <v>6536590</v>
+        <v>6536384</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5703,13 +5710,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635095</t>
+          <t>https://artportalen.se/Sighting/120635120</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120635096</v>
+        <v>120635095</v>
       </c>
       <c r="B44" t="n">
         <v>5179</v>
@@ -5753,10 +5760,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>517630</v>
+        <v>517618</v>
       </c>
       <c r="R44" t="n">
-        <v>6536573</v>
+        <v>6536590</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5825,13 +5832,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635096</t>
+          <t>https://artportalen.se/Sighting/120635095</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120635118</v>
+        <v>120635096</v>
       </c>
       <c r="B45" t="n">
         <v>5179</v>
@@ -5871,14 +5878,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>517614</v>
+        <v>517630</v>
       </c>
       <c r="R45" t="n">
-        <v>6536378</v>
+        <v>6536573</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5947,13 +5954,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635118</t>
+          <t>https://artportalen.se/Sighting/120635096</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120635184</v>
+        <v>120635118</v>
       </c>
       <c r="B46" t="n">
         <v>5179</v>
@@ -5997,10 +6004,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517640</v>
+        <v>517614</v>
       </c>
       <c r="R46" t="n">
-        <v>6536207</v>
+        <v>6536378</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6069,38 +6076,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635184</t>
+          <t>https://artportalen.se/Sighting/120635118</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120635188</v>
+        <v>120635184</v>
       </c>
       <c r="B47" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6109,7 +6116,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6119,10 +6126,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517619</v>
+        <v>517640</v>
       </c>
       <c r="R47" t="n">
-        <v>6536148</v>
+        <v>6536207</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6191,16 +6198,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635188</t>
+          <t>https://artportalen.se/Sighting/120635184</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120635114</v>
+        <v>120635188</v>
       </c>
       <c r="B48" t="n">
-        <v>5178</v>
+        <v>5495</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6208,21 +6215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102204</v>
+        <v>101410</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6237,14 +6244,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517596</v>
+        <v>517619</v>
       </c>
       <c r="R48" t="n">
-        <v>6536395</v>
+        <v>6536148</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6313,38 +6320,38 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635114</t>
+          <t>https://artportalen.se/Sighting/120635188</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120635124</v>
+        <v>120635114</v>
       </c>
       <c r="B49" t="n">
-        <v>4781</v>
+        <v>5178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102306</v>
+        <v>102204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6353,20 +6360,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517623</v>
+        <v>517596</v>
       </c>
       <c r="R49" t="n">
-        <v>6536362</v>
+        <v>6536395</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6411,11 +6418,6 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6440,16 +6442,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635124</t>
+          <t>https://artportalen.se/Sighting/120635114</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120635104</v>
+        <v>120635124</v>
       </c>
       <c r="B50" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6457,21 +6459,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6480,20 +6482,20 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517609</v>
+        <v>517623</v>
       </c>
       <c r="R50" t="n">
-        <v>6536542</v>
+        <v>6536362</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6538,6 +6540,11 @@
           <t>16:00</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6562,13 +6569,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635104</t>
+          <t>https://artportalen.se/Sighting/120635124</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120635119</v>
+        <v>120635104</v>
       </c>
       <c r="B51" t="n">
         <v>5199</v>
@@ -6602,20 +6609,20 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517619</v>
+        <v>517609</v>
       </c>
       <c r="R51" t="n">
-        <v>6536384</v>
+        <v>6536542</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6684,13 +6691,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635119</t>
+          <t>https://artportalen.se/Sighting/120635104</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120635176</v>
+        <v>120635119</v>
       </c>
       <c r="B52" t="n">
         <v>5199</v>
@@ -6724,7 +6731,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6734,10 +6741,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517661</v>
+        <v>517619</v>
       </c>
       <c r="R52" t="n">
-        <v>6536283</v>
+        <v>6536384</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6806,13 +6813,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635176</t>
+          <t>https://artportalen.se/Sighting/120635119</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120635190</v>
+        <v>120635176</v>
       </c>
       <c r="B53" t="n">
         <v>5199</v>
@@ -6856,10 +6863,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517634</v>
+        <v>517661</v>
       </c>
       <c r="R53" t="n">
-        <v>6536147</v>
+        <v>6536283</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6928,16 +6935,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635190</t>
+          <t>https://artportalen.se/Sighting/120635176</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120635112</v>
+        <v>120635190</v>
       </c>
       <c r="B54" t="n">
-        <v>97983</v>
+        <v>5199</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6945,42 +6952,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517607</v>
+        <v>517634</v>
       </c>
       <c r="R54" t="n">
-        <v>6536479</v>
+        <v>6536147</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7049,58 +7057,59 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635112</t>
+          <t>https://artportalen.se/Sighting/120635190</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120635183</v>
+        <v>120635112</v>
       </c>
       <c r="B55" t="n">
-        <v>79085</v>
+        <v>97983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517625</v>
+        <v>517607</v>
       </c>
       <c r="R55" t="n">
-        <v>6536200</v>
+        <v>6536479</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7169,63 +7178,61 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635183</t>
+          <t>https://artportalen.se/Sighting/120635112</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132585613</v>
+        <v>120635183</v>
       </c>
       <c r="B56" t="n">
-        <v>40305</v>
+        <v>79085</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>214803</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kortorpa mosse, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>515594</v>
+        <v>517625</v>
       </c>
       <c r="R56" t="n">
-        <v>6537089</v>
+        <v>6536200</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7249,12 +7256,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7281,51 +7298,60 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132585613</t>
+          <t>https://artportalen.se/Sighting/120635183</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>85451244</v>
+        <v>132585613</v>
       </c>
       <c r="B57" t="n">
-        <v>97358</v>
+        <v>40305</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>214803</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Kortorpa mosse, Nrk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519672</v>
+        <v>515594</v>
       </c>
       <c r="R57" t="n">
-        <v>6532590</v>
+        <v>6537089</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7352,12 +7378,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7366,30 +7392,31 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451244</t>
+          <t>https://artportalen.se/Sighting/132585613</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>85451245</v>
+        <v>85451244</v>
       </c>
       <c r="B58" t="n">
         <v>97358</v>
@@ -7424,10 +7451,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519625</v>
+        <v>519672</v>
       </c>
       <c r="R58" t="n">
-        <v>6532581</v>
+        <v>6532590</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7485,16 +7512,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451245</t>
+          <t>https://artportalen.se/Sighting/85451244</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>55321736</v>
+        <v>85451245</v>
       </c>
       <c r="B59" t="n">
-        <v>78993</v>
+        <v>97358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7502,41 +7529,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519636</v>
+        <v>519625</v>
       </c>
       <c r="R59" t="n">
-        <v>6532709</v>
+        <v>6532581</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7560,17 +7583,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7583,72 +7601,71 @@
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321736</t>
+          <t>https://artportalen.se/Sighting/85451245</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>85451302</v>
+        <v>55321736</v>
       </c>
       <c r="B60" t="n">
-        <v>96458</v>
+        <v>78993</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2818</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519731</v>
+        <v>519636</v>
       </c>
       <c r="R60" t="n">
-        <v>6532645</v>
+        <v>6532709</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7672,12 +7689,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7690,29 +7712,34 @@
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451302</t>
+          <t>https://artportalen.se/Sighting/55321736</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>85451356</v>
+        <v>85451302</v>
       </c>
       <c r="B61" t="n">
-        <v>92333</v>
+        <v>96458</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7720,21 +7747,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4217</v>
+        <v>2818</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7744,10 +7771,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519697</v>
+        <v>519731</v>
       </c>
       <c r="R61" t="n">
-        <v>6532776</v>
+        <v>6532645</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7805,54 +7832,54 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451356</t>
+          <t>https://artportalen.se/Sighting/85451302</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>54013950</v>
+        <v>85451356</v>
       </c>
       <c r="B62" t="n">
-        <v>93197</v>
+        <v>92333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519596</v>
+        <v>519697</v>
       </c>
       <c r="R62" t="n">
-        <v>6532710</v>
+        <v>6532776</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7876,12 +7903,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7893,28 +7920,27 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AR62" t="inlineStr"/>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54013950</t>
+          <t>https://artportalen.se/Sighting/85451356</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>81095228</v>
+        <v>54013950</v>
       </c>
       <c r="B63" t="n">
         <v>93197</v>
@@ -7945,14 +7971,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hjärtasjön med omnejd, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519615</v>
+        <v>519596</v>
       </c>
       <c r="R63" t="n">
-        <v>6532734</v>
+        <v>6532710</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7979,12 +8005,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7996,65 +8022,66 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AR63" t="inlineStr"/>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81095228</t>
+          <t>https://artportalen.se/Sighting/54013950</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>54013984</v>
+        <v>81095228</v>
       </c>
       <c r="B64" t="n">
-        <v>91282</v>
+        <v>93197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>Hjärtasjön med omnejd, Nrk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519636</v>
+        <v>519615</v>
       </c>
       <c r="R64" t="n">
-        <v>6532709</v>
+        <v>6532734</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8081,12 +8108,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8098,76 +8125,68 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AR64" t="inlineStr"/>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54013984</t>
+          <t>https://artportalen.se/Sighting/81095228</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132028911</v>
+        <v>54013984</v>
       </c>
       <c r="B65" t="n">
-        <v>79373</v>
+        <v>91282</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bavlingeskogen, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519619</v>
+        <v>519636</v>
       </c>
       <c r="R65" t="n">
-        <v>6532722</v>
+        <v>6532709</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8191,12 +8210,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8205,76 +8224,79 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
+      <c r="AR65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132028911</t>
+          <t>https://artportalen.se/Sighting/54013984</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>55321959</v>
+        <v>132028911</v>
       </c>
       <c r="B66" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Bavlingeskogen, Nrk</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519636</v>
+        <v>519619</v>
       </c>
       <c r="R66" t="n">
-        <v>6532709</v>
+        <v>6532722</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8298,17 +8320,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8317,35 +8334,31 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321959</t>
+          <t>https://artportalen.se/Sighting/132028911</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55321978</v>
+        <v>55321959</v>
       </c>
       <c r="B67" t="n">
         <v>79946</v>
@@ -8384,10 +8397,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519596</v>
+        <v>519636</v>
       </c>
       <c r="R67" t="n">
-        <v>6532710</v>
+        <v>6532709</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8455,13 +8468,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321978</t>
+          <t>https://artportalen.se/Sighting/55321959</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>55322041</v>
+        <v>55321978</v>
       </c>
       <c r="B68" t="n">
         <v>79946</v>
@@ -8500,10 +8513,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519628</v>
+        <v>519596</v>
       </c>
       <c r="R68" t="n">
-        <v>6532734</v>
+        <v>6532710</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8540,7 +8553,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Observerad av Toni Berglund</t>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8571,13 +8584,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322041</t>
+          <t>https://artportalen.se/Sighting/55321978</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>85451274</v>
+        <v>55322041</v>
       </c>
       <c r="B69" t="n">
         <v>79946</v>
@@ -8605,20 +8618,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519738</v>
+        <v>519628</v>
       </c>
       <c r="R69" t="n">
-        <v>6532781</v>
+        <v>6532734</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8642,12 +8659,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Observerad av Toni Berglund</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8660,29 +8682,34 @@
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451274</t>
+          <t>https://artportalen.se/Sighting/55322041</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>85451350</v>
+        <v>85451274</v>
       </c>
       <c r="B70" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8690,21 +8717,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8714,10 +8741,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520143</v>
+        <v>519738</v>
       </c>
       <c r="R70" t="n">
-        <v>6532731</v>
+        <v>6532781</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8775,16 +8802,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451350</t>
+          <t>https://artportalen.se/Sighting/85451274</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>85451285</v>
+        <v>85451350</v>
       </c>
       <c r="B71" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8792,21 +8819,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8816,10 +8843,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520192</v>
+        <v>520143</v>
       </c>
       <c r="R71" t="n">
-        <v>6532728</v>
+        <v>6532731</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8877,13 +8904,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451285</t>
+          <t>https://artportalen.se/Sighting/85451350</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>85451403</v>
+        <v>85451285</v>
       </c>
       <c r="B72" t="n">
         <v>79946</v>
@@ -8914,14 +8941,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>ost Bavlingssjön, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520311</v>
+        <v>520192</v>
       </c>
       <c r="R72" t="n">
-        <v>6532603</v>
+        <v>6532728</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8979,54 +9006,54 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451403</t>
+          <t>https://artportalen.se/Sighting/85451285</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>80563800</v>
+        <v>85451403</v>
       </c>
       <c r="B73" t="n">
-        <v>93193</v>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4363</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>ost Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519723</v>
+        <v>520311</v>
       </c>
       <c r="R73" t="n">
-        <v>6531341</v>
+        <v>6532603</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9050,12 +9077,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9070,49 +9097,49 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563800</t>
+          <t>https://artportalen.se/Sighting/85451403</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>80563801</v>
+        <v>80563800</v>
       </c>
       <c r="B74" t="n">
-        <v>93197</v>
+        <v>93193</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9122,10 +9149,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519697</v>
+        <v>519723</v>
       </c>
       <c r="R74" t="n">
-        <v>6531333</v>
+        <v>6531341</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9183,13 +9210,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563801</t>
+          <t>https://artportalen.se/Sighting/80563800</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>80563803</v>
+        <v>80563801</v>
       </c>
       <c r="B75" t="n">
         <v>93197</v>
@@ -9224,10 +9251,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519682</v>
+        <v>519697</v>
       </c>
       <c r="R75" t="n">
-        <v>6531348</v>
+        <v>6531333</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9285,13 +9312,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563803</t>
+          <t>https://artportalen.se/Sighting/80563801</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>80563804</v>
+        <v>80563803</v>
       </c>
       <c r="B76" t="n">
         <v>93197</v>
@@ -9326,10 +9353,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519675</v>
+        <v>519682</v>
       </c>
       <c r="R76" t="n">
-        <v>6531363</v>
+        <v>6531348</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9387,13 +9414,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563804</t>
+          <t>https://artportalen.se/Sighting/80563803</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>80563805</v>
+        <v>80563804</v>
       </c>
       <c r="B77" t="n">
         <v>93197</v>
@@ -9428,10 +9455,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519682</v>
+        <v>519675</v>
       </c>
       <c r="R77" t="n">
-        <v>6531371</v>
+        <v>6531363</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9489,51 +9516,51 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563805</t>
+          <t>https://artportalen.se/Sighting/80563804</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>54014169</v>
+        <v>80563805</v>
       </c>
       <c r="B78" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519821</v>
+        <v>519682</v>
       </c>
       <c r="R78" t="n">
-        <v>6531449</v>
+        <v>6531371</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9560,12 +9587,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9577,28 +9604,27 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AR78" t="inlineStr"/>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54014169</t>
+          <t>https://artportalen.se/Sighting/80563805</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>85451261</v>
+        <v>54014169</v>
       </c>
       <c r="B79" t="n">
         <v>91872</v>
@@ -9629,17 +9655,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519855</v>
+        <v>519821</v>
       </c>
       <c r="R79" t="n">
-        <v>6531422</v>
+        <v>6531449</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9663,12 +9689,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9680,72 +9706,69 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
+      <c r="AR79" t="inlineStr"/>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451261</t>
+          <t>https://artportalen.se/Sighting/54014169</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>55322013</v>
+        <v>85451261</v>
       </c>
       <c r="B80" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519789</v>
+        <v>519855</v>
       </c>
       <c r="R80" t="n">
-        <v>6531472</v>
+        <v>6531422</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9769,17 +9792,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9792,31 +9810,26 @@
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322013</t>
+          <t>https://artportalen.se/Sighting/85451261</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80563802</v>
+        <v>55322013</v>
       </c>
       <c r="B81" t="n">
         <v>79946</v>
@@ -9844,17 +9857,21 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>519687</v>
+        <v>519789</v>
       </c>
       <c r="R81" t="n">
-        <v>6531345</v>
+        <v>6531472</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9881,12 +9898,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9898,32 +9920,32 @@
       <c r="AG81" t="b">
         <v>0</v>
       </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>silverstubbe</t>
-        </is>
-      </c>
       <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563802</t>
+          <t>https://artportalen.se/Sighting/55322013</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>85451281</v>
+        <v>80563802</v>
       </c>
       <c r="B82" t="n">
         <v>79946</v>
@@ -9954,17 +9976,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>519882</v>
+        <v>519687</v>
       </c>
       <c r="R82" t="n">
-        <v>6531425</v>
+        <v>6531345</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9988,12 +10010,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10004,20 +10026,127 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>silverstubbe</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563802</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>85451281</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>väst Bavlingssjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>519882</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6531425</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2020-05-03</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/85451281</t>
         </is>
@@ -10106,6 +10235,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136646193</v>
       </c>
       <c r="B10" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>115377556</v>
       </c>
       <c r="B11" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>115377695</v>
       </c>
       <c r="B12" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>129810219</v>
       </c>
       <c r="B25" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         <v>120635120</v>
       </c>
       <c r="B43" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ83"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,52 +1491,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115377672</v>
+        <v>137166501</v>
       </c>
       <c r="B9" t="n">
-        <v>93197</v>
+        <v>57195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skepphultamossen, Nrk</t>
+          <t>Haddebo/Sjölunda, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516862</v>
+        <v>516688</v>
       </c>
       <c r="R9" t="n">
-        <v>6540377</v>
+        <v>6540856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,22 +1556,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tjäderspillning. Ej Spelhäll</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,70 +1575,64 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Amanda Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377672</t>
+          <t>https://artportalen.se/Sighting/137166501</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136646193</v>
+        <v>115377672</v>
       </c>
       <c r="B10" t="n">
-        <v>57195</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1658,13 +1640,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516931</v>
+        <v>516862</v>
       </c>
       <c r="R10" t="n">
-        <v>6540289</v>
+        <v>6540377</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,27 +1670,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>20:15, i SV, landar 50 m bort, rapar</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,33 +1694,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136646193</t>
+          <t>https://artportalen.se/Sighting/115377672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115377556</v>
+        <v>136646193</v>
       </c>
       <c r="B11" t="n">
-        <v>4777</v>
+        <v>57195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,32 +1729,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1784,13 +1765,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517017</v>
+        <v>516931</v>
       </c>
       <c r="R11" t="n">
-        <v>6540497</v>
+        <v>6540289</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1814,22 +1795,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>20:15, i SV, landar 50 m bort, rapar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,34 +1824,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Amanda Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377556</t>
+          <t>https://artportalen.se/Sighting/136646193</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115377695</v>
+        <v>137166519</v>
       </c>
       <c r="B12" t="n">
-        <v>4777</v>
+        <v>57195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,43 +1858,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skepphultamossen, Nrk</t>
+          <t>Haddebo/Sjölunda, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517002</v>
+        <v>516949</v>
       </c>
       <c r="R12" t="n">
-        <v>6540481</v>
+        <v>6540377</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,22 +1912,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fem spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,34 +1931,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Amanda Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377695</t>
+          <t>https://artportalen.se/Sighting/137166519</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115377558</v>
+        <v>115377556</v>
       </c>
       <c r="B13" t="n">
-        <v>5179</v>
+        <v>4777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,21 +1965,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2100,16 +2070,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115377558</t>
+          <t>https://artportalen.se/Sighting/115377556</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129810216</v>
+        <v>115377695</v>
       </c>
       <c r="B14" t="n">
-        <v>97983</v>
+        <v>4777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,45 +2087,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vedkärret, Nrk</t>
+          <t>Skepphultamossen, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521391</v>
+        <v>517002</v>
       </c>
       <c r="R14" t="n">
-        <v>6539013</v>
+        <v>6540481</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2179,17 +2150,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2215,22 +2186,22 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810216</t>
+          <t>https://artportalen.se/Sighting/115377695</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133708635</v>
+        <v>115377558</v>
       </c>
       <c r="B15" t="n">
-        <v>58308</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,46 +2209,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103008</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rösjön, Rösjön, Nrk</t>
+          <t>Skepphultamossen, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516741</v>
+        <v>517017</v>
       </c>
       <c r="R15" t="n">
-        <v>6539120</v>
+        <v>6540497</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2301,22 +2272,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,33 +2296,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133708635</t>
+          <t>https://artportalen.se/Sighting/115377558</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134855725</v>
+        <v>129810216</v>
       </c>
       <c r="B16" t="n">
-        <v>99210</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,51 +2331,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stakgölsmossen, Nrk</t>
+          <t>Vedkärret, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>516726</v>
+        <v>521391</v>
       </c>
       <c r="R16" t="n">
-        <v>6538929</v>
+        <v>6539013</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2427,12 +2393,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2441,33 +2417,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134855725</t>
+          <t>https://artportalen.se/Sighting/129810216</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97155205</v>
+        <v>133708635</v>
       </c>
       <c r="B17" t="n">
-        <v>97983</v>
+        <v>58308</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,41 +2452,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>103008</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stakgölsmossen, Nrk</t>
+          <t>Rösjön, Rösjön, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>516810</v>
+        <v>516741</v>
       </c>
       <c r="R17" t="n">
-        <v>6538951</v>
+        <v>6539120</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2533,17 +2515,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2552,34 +2539,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97155205</t>
+          <t>https://artportalen.se/Sighting/133708635</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108401900</v>
+        <v>134855725</v>
       </c>
       <c r="B18" t="n">
-        <v>96708</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,42 +2573,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tärnmossemon, Nrk</t>
+          <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520654</v>
+        <v>516726</v>
       </c>
       <c r="R18" t="n">
-        <v>6538974</v>
+        <v>6538929</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,22 +2641,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,34 +2655,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108401900</t>
+          <t>https://artportalen.se/Sighting/134855725</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>62126985</v>
+        <v>97155205</v>
       </c>
       <c r="B19" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,16 +2689,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2726,16 +2707,20 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skåle 0850/5550, Nrk</t>
+          <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511839</v>
+        <v>516810</v>
       </c>
       <c r="R19" t="n">
-        <v>6538728</v>
+        <v>6538951</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2757,22 +2742,22 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Sparsamt</t>
+          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2781,33 +2766,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62126985</t>
+          <t>https://artportalen.se/Sighting/97155205</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98669244</v>
+        <v>108401900</v>
       </c>
       <c r="B20" t="n">
-        <v>96554</v>
+        <v>96708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,31 +2801,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2847,14 +2829,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gropadalen, Nrk</t>
+          <t>Tärnmossemon, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509662</v>
+        <v>520654</v>
       </c>
       <c r="R20" t="n">
-        <v>6538673</v>
+        <v>6538974</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2876,17 +2858,27 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,66 +2905,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98669244</t>
+          <t>https://artportalen.se/Sighting/108401900</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135018500</v>
+        <v>62126985</v>
       </c>
       <c r="B21" t="n">
-        <v>58141</v>
+        <v>97986</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hovdesjön. bäcken, Nrk</t>
+          <t>Skåle 0850/5550, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>512422</v>
+        <v>511839</v>
       </c>
       <c r="R21" t="n">
-        <v>6538962</v>
+        <v>6538728</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2996,22 +2976,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>1984-12-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>1984-12-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,27 +3001,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135018500</t>
+          <t>https://artportalen.se/Sighting/62126985</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135018493</v>
+        <v>98669244</v>
       </c>
       <c r="B22" t="n">
-        <v>58136</v>
+        <v>96554</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,46 +3029,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103023</v>
+        <v>210</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hovdesjön. bäcken, Nrk</t>
+          <t>Gropadalen, Nrk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>512422</v>
+        <v>509662</v>
       </c>
       <c r="R22" t="n">
-        <v>6538962</v>
+        <v>6538673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3120,22 +3095,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3144,79 +3109,84 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135018493</t>
+          <t>https://artportalen.se/Sighting/98669244</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129810221</v>
+        <v>135018500</v>
       </c>
       <c r="B23" t="n">
-        <v>97394</v>
+        <v>58141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2590</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Aggsjön, Nrk</t>
+          <t>Hovdesjön. bäcken, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521076</v>
+        <v>512422</v>
       </c>
       <c r="R23" t="n">
-        <v>6538419</v>
+        <v>6538962</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3235,12 +3205,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3250,12 +3220,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3264,51 +3234,50 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810221</t>
+          <t>https://artportalen.se/Sighting/135018500</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129810223</v>
+        <v>135018493</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>58136</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103023</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3316,28 +3285,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Aggsjön, Nrk</t>
+          <t>Hovdesjön. bäcken, Nrk</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521077</v>
+        <v>512422</v>
       </c>
       <c r="R24" t="n">
-        <v>6538398</v>
+        <v>6538962</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3356,12 +3329,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3371,17 +3344,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3396,27 +3364,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810223</t>
+          <t>https://artportalen.se/Sighting/135018493</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129810219</v>
+        <v>129810221</v>
       </c>
       <c r="B25" t="n">
-        <v>4777</v>
+        <v>97394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3424,32 +3392,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3457,7 +3424,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521090</v>
+        <v>521076</v>
       </c>
       <c r="R25" t="n">
         <v>6538419</v>
@@ -3529,47 +3496,46 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810219</t>
+          <t>https://artportalen.se/Sighting/129810221</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129810218</v>
+        <v>129810223</v>
       </c>
       <c r="B26" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3579,10 +3545,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521090</v>
+        <v>521077</v>
       </c>
       <c r="R26" t="n">
-        <v>6538419</v>
+        <v>6538398</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3627,13 +3593,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3651,16 +3621,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810218</t>
+          <t>https://artportalen.se/Sighting/129810223</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129810217</v>
+        <v>129810219</v>
       </c>
       <c r="B27" t="n">
-        <v>97983</v>
+        <v>4777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,31 +3638,32 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3700,10 +3671,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521141</v>
+        <v>521090</v>
       </c>
       <c r="R27" t="n">
-        <v>6538398</v>
+        <v>6538419</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3772,69 +3743,63 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810217</t>
+          <t>https://artportalen.se/Sighting/129810219</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67277679</v>
+        <v>129810218</v>
       </c>
       <c r="B28" t="n">
-        <v>109866</v>
+        <v>5179</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220228</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kållslätt, 525 m NNO om, Nrk</t>
+          <t>Aggsjön, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510443</v>
+        <v>521090</v>
       </c>
       <c r="R28" t="n">
-        <v>6538515</v>
+        <v>6538419</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3853,22 +3818,27 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Hal-0031</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,84 +3847,77 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Skogsvägkant</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67277679</t>
+          <t>https://artportalen.se/Sighting/129810218</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128760477</v>
+        <v>129810217</v>
       </c>
       <c r="B29" t="n">
-        <v>93197</v>
+        <v>97983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gruvemon, Nrk</t>
+          <t>Aggsjön, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517886</v>
+        <v>521141</v>
       </c>
       <c r="R29" t="n">
-        <v>6536773</v>
+        <v>6538398</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3981,22 +3944,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4023,16 +3986,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760477</t>
+          <t>https://artportalen.se/Sighting/129810217</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120432305</v>
+        <v>67277679</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>109866</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4040,41 +4003,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>220228</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
+          <t>Kållslätt, 525 m NNO om, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518189</v>
+        <v>510443</v>
       </c>
       <c r="R30" t="n">
-        <v>6536658</v>
+        <v>6538515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4096,27 +4067,22 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Hal-0031</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4125,34 +4091,42 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Skogsvägkant</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432305</t>
+          <t>https://artportalen.se/Sighting/67277679</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120432283</v>
+        <v>128760477</v>
       </c>
       <c r="B31" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4160,44 +4134,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
+          <t>Gruvemon, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518189</v>
+        <v>517886</v>
       </c>
       <c r="R31" t="n">
-        <v>6536658</v>
+        <v>6536773</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4221,22 +4195,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4263,16 +4237,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432283</t>
+          <t>https://artportalen.se/Sighting/128760477</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120432395</v>
+        <v>120432305</v>
       </c>
       <c r="B32" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4280,21 +4254,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4307,14 +4281,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fåglamossen, Nrk</t>
+          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518363</v>
+        <v>518189</v>
       </c>
       <c r="R32" t="n">
-        <v>6536679</v>
+        <v>6536658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4383,59 +4357,58 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432395</t>
+          <t>https://artportalen.se/Sighting/120432305</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115463834</v>
+        <v>120432283</v>
       </c>
       <c r="B33" t="n">
-        <v>97394</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ommekärrsmossen, Nrk</t>
+          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521356</v>
+        <v>518189</v>
       </c>
       <c r="R33" t="n">
-        <v>6536843</v>
+        <v>6536658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4462,22 +4435,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4504,59 +4477,58 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463834</t>
+          <t>https://artportalen.se/Sighting/120432283</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115464064</v>
+        <v>120432395</v>
       </c>
       <c r="B34" t="n">
-        <v>97394</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ommekärrsmossen, Nrk</t>
+          <t>Fåglamossen, Nrk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521284</v>
+        <v>518363</v>
       </c>
       <c r="R34" t="n">
-        <v>6536870</v>
+        <v>6536679</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4583,22 +4555,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4625,16 +4597,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115464064</t>
+          <t>https://artportalen.se/Sighting/120432395</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115463863</v>
+        <v>137168022</v>
       </c>
       <c r="B35" t="n">
-        <v>92333</v>
+        <v>57195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4642,41 +4614,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4217</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ommekärrsmossen, Nrk</t>
+          <t>Haddebo/Sjölunda, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521375</v>
+        <v>518036</v>
       </c>
       <c r="R35" t="n">
-        <v>6536833</v>
+        <v>6536899</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4703,22 +4668,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>3 ostbågar. Möjligen spelhäll</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4727,34 +4687,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463863</t>
+          <t>https://artportalen.se/Sighting/137168022</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115463816</v>
+        <v>115463834</v>
       </c>
       <c r="B36" t="n">
-        <v>5179</v>
+        <v>97394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4762,32 +4721,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>2590</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4795,10 +4753,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521348</v>
+        <v>521356</v>
       </c>
       <c r="R36" t="n">
-        <v>6536870</v>
+        <v>6536843</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4867,13 +4825,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463816</t>
+          <t>https://artportalen.se/Sighting/115463834</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120635109</v>
+        <v>115464064</v>
       </c>
       <c r="B37" t="n">
         <v>97394</v>
@@ -4912,14 +4870,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Ommekärrsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517608</v>
+        <v>521284</v>
       </c>
       <c r="R37" t="n">
-        <v>6536616</v>
+        <v>6536870</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4946,22 +4904,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4988,16 +4946,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635109</t>
+          <t>https://artportalen.se/Sighting/115464064</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120635189</v>
+        <v>115463863</v>
       </c>
       <c r="B38" t="n">
-        <v>91872</v>
+        <v>92333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5005,21 +4963,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5032,14 +4990,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Ommekärrsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>517634</v>
+        <v>521375</v>
       </c>
       <c r="R38" t="n">
-        <v>6536147</v>
+        <v>6536833</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5066,22 +5024,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5108,58 +5066,60 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635189</t>
+          <t>https://artportalen.se/Sighting/115463863</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120635175</v>
+        <v>115463816</v>
       </c>
       <c r="B39" t="n">
-        <v>93235</v>
+        <v>5179</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Ommekärrsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>517662</v>
+        <v>521348</v>
       </c>
       <c r="R39" t="n">
-        <v>6536294</v>
+        <v>6536870</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5186,22 +5146,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5228,58 +5188,59 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635175</t>
+          <t>https://artportalen.se/Sighting/115463816</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120635132</v>
+        <v>120635109</v>
       </c>
       <c r="B40" t="n">
-        <v>75428</v>
+        <v>97394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>517612</v>
+        <v>517608</v>
       </c>
       <c r="R40" t="n">
-        <v>6536339</v>
+        <v>6536616</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5348,44 +5309,44 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635132</t>
+          <t>https://artportalen.se/Sighting/120635109</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120635182</v>
+        <v>120635189</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5396,10 +5357,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517625</v>
+        <v>517634</v>
       </c>
       <c r="R41" t="n">
-        <v>6536200</v>
+        <v>6536147</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5468,16 +5429,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635182</t>
+          <t>https://artportalen.se/Sighting/120635189</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120635185</v>
+        <v>120635175</v>
       </c>
       <c r="B42" t="n">
-        <v>79946</v>
+        <v>93235</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,27 +5446,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5516,10 +5477,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>517623</v>
+        <v>517662</v>
       </c>
       <c r="R42" t="n">
-        <v>6536181</v>
+        <v>6536294</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5588,60 +5549,58 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635185</t>
+          <t>https://artportalen.se/Sighting/120635175</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120635120</v>
+        <v>120635132</v>
       </c>
       <c r="B43" t="n">
-        <v>4777</v>
+        <v>75428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>517619</v>
+        <v>517612</v>
       </c>
       <c r="R43" t="n">
-        <v>6536384</v>
+        <v>6536339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5710,60 +5669,58 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635120</t>
+          <t>https://artportalen.se/Sighting/120635132</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120635095</v>
+        <v>120635182</v>
       </c>
       <c r="B44" t="n">
-        <v>5179</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>517618</v>
+        <v>517625</v>
       </c>
       <c r="R44" t="n">
-        <v>6536590</v>
+        <v>6536200</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5832,60 +5789,58 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635095</t>
+          <t>https://artportalen.se/Sighting/120635182</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120635096</v>
+        <v>120635185</v>
       </c>
       <c r="B45" t="n">
-        <v>5179</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>517630</v>
+        <v>517623</v>
       </c>
       <c r="R45" t="n">
-        <v>6536573</v>
+        <v>6536181</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5954,16 +5909,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635096</t>
+          <t>https://artportalen.se/Sighting/120635185</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120635118</v>
+        <v>120635120</v>
       </c>
       <c r="B46" t="n">
-        <v>5179</v>
+        <v>4777</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5971,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6004,10 +5959,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517614</v>
+        <v>517619</v>
       </c>
       <c r="R46" t="n">
-        <v>6536378</v>
+        <v>6536384</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6076,13 +6031,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635118</t>
+          <t>https://artportalen.se/Sighting/120635120</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120635184</v>
+        <v>120635095</v>
       </c>
       <c r="B47" t="n">
         <v>5179</v>
@@ -6122,14 +6077,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517640</v>
+        <v>517618</v>
       </c>
       <c r="R47" t="n">
-        <v>6536207</v>
+        <v>6536590</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6198,38 +6153,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635184</t>
+          <t>https://artportalen.se/Sighting/120635095</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120635188</v>
+        <v>120635096</v>
       </c>
       <c r="B48" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6238,20 +6193,20 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517619</v>
+        <v>517630</v>
       </c>
       <c r="R48" t="n">
-        <v>6536148</v>
+        <v>6536573</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6320,38 +6275,38 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635188</t>
+          <t>https://artportalen.se/Sighting/120635096</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120635114</v>
+        <v>120635118</v>
       </c>
       <c r="B49" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102204</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6360,20 +6315,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517596</v>
+        <v>517614</v>
       </c>
       <c r="R49" t="n">
-        <v>6536395</v>
+        <v>6536378</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6442,16 +6397,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635114</t>
+          <t>https://artportalen.se/Sighting/120635118</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120635124</v>
+        <v>120635184</v>
       </c>
       <c r="B50" t="n">
-        <v>4781</v>
+        <v>5179</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6459,21 +6414,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6492,10 +6447,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517623</v>
+        <v>517640</v>
       </c>
       <c r="R50" t="n">
-        <v>6536362</v>
+        <v>6536207</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6540,11 +6495,6 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6569,38 +6519,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635124</t>
+          <t>https://artportalen.se/Sighting/120635184</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120635104</v>
+        <v>120635188</v>
       </c>
       <c r="B51" t="n">
-        <v>5199</v>
+        <v>5495</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>101410</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6615,14 +6565,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517609</v>
+        <v>517619</v>
       </c>
       <c r="R51" t="n">
-        <v>6536542</v>
+        <v>6536148</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6691,38 +6641,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635104</t>
+          <t>https://artportalen.se/Sighting/120635188</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120635119</v>
+        <v>120635114</v>
       </c>
       <c r="B52" t="n">
-        <v>5199</v>
+        <v>5178</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>102204</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6731,20 +6681,20 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517619</v>
+        <v>517596</v>
       </c>
       <c r="R52" t="n">
-        <v>6536384</v>
+        <v>6536395</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6813,16 +6763,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635119</t>
+          <t>https://artportalen.se/Sighting/120635114</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120635176</v>
+        <v>120635124</v>
       </c>
       <c r="B53" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6830,21 +6780,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6853,7 +6803,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6863,10 +6813,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517661</v>
+        <v>517623</v>
       </c>
       <c r="R53" t="n">
-        <v>6536283</v>
+        <v>6536362</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6911,6 +6861,11 @@
           <t>16:00</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6935,13 +6890,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635176</t>
+          <t>https://artportalen.se/Sighting/120635124</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120635190</v>
+        <v>120635104</v>
       </c>
       <c r="B54" t="n">
         <v>5199</v>
@@ -6981,14 +6936,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517634</v>
+        <v>517609</v>
       </c>
       <c r="R54" t="n">
-        <v>6536147</v>
+        <v>6536542</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7057,16 +7012,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635190</t>
+          <t>https://artportalen.se/Sighting/120635104</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120635112</v>
+        <v>120635119</v>
       </c>
       <c r="B55" t="n">
-        <v>97983</v>
+        <v>5199</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7074,42 +7029,43 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517607</v>
+        <v>517619</v>
       </c>
       <c r="R55" t="n">
-        <v>6536479</v>
+        <v>6536384</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7178,47 +7134,49 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635112</t>
+          <t>https://artportalen.se/Sighting/120635119</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120635183</v>
+        <v>120635176</v>
       </c>
       <c r="B56" t="n">
-        <v>79085</v>
+        <v>5199</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7226,10 +7184,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517625</v>
+        <v>517661</v>
       </c>
       <c r="R56" t="n">
-        <v>6536200</v>
+        <v>6536283</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7298,16 +7256,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635183</t>
+          <t>https://artportalen.se/Sighting/120635176</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132585613</v>
+        <v>120635190</v>
       </c>
       <c r="B57" t="n">
-        <v>40305</v>
+        <v>5199</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7315,21 +7273,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>214803</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7344,17 +7302,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kortorpa mosse, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>515594</v>
+        <v>517634</v>
       </c>
       <c r="R57" t="n">
-        <v>6537089</v>
+        <v>6536147</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7378,12 +7336,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7410,54 +7378,62 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132585613</t>
+          <t>https://artportalen.se/Sighting/120635190</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>85451244</v>
+        <v>120635112</v>
       </c>
       <c r="B58" t="n">
-        <v>97358</v>
+        <v>97983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519672</v>
+        <v>517607</v>
       </c>
       <c r="R58" t="n">
-        <v>6532590</v>
+        <v>6536479</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7481,12 +7457,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7495,33 +7481,34 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451244</t>
+          <t>https://artportalen.se/Sighting/120635112</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>85451245</v>
+        <v>120635183</v>
       </c>
       <c r="B59" t="n">
-        <v>97358</v>
+        <v>79085</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7529,37 +7516,44 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519625</v>
+        <v>517625</v>
       </c>
       <c r="R59" t="n">
-        <v>6532581</v>
+        <v>6536200</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7583,12 +7577,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7597,75 +7601,81 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451245</t>
+          <t>https://artportalen.se/Sighting/120635183</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>55321736</v>
+        <v>132585613</v>
       </c>
       <c r="B60" t="n">
-        <v>78993</v>
+        <v>40305</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>214803</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Borkhausen, 1789)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Kortorpa mosse, Nrk</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519636</v>
+        <v>515594</v>
       </c>
       <c r="R60" t="n">
-        <v>6532709</v>
+        <v>6537089</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7689,17 +7699,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7708,60 +7713,56 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321736</t>
+          <t>https://artportalen.se/Sighting/132585613</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>85451302</v>
+        <v>85451244</v>
       </c>
       <c r="B61" t="n">
-        <v>96458</v>
+        <v>97358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2818</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7771,10 +7772,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519731</v>
+        <v>519672</v>
       </c>
       <c r="R61" t="n">
-        <v>6532645</v>
+        <v>6532590</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7832,38 +7833,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451302</t>
+          <t>https://artportalen.se/Sighting/85451244</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>85451356</v>
+        <v>85451245</v>
       </c>
       <c r="B62" t="n">
-        <v>92333</v>
+        <v>97358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4217</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7873,10 +7874,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519697</v>
+        <v>519625</v>
       </c>
       <c r="R62" t="n">
-        <v>6532776</v>
+        <v>6532581</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7934,16 +7935,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451356</t>
+          <t>https://artportalen.se/Sighting/85451245</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>54013950</v>
+        <v>55321736</v>
       </c>
       <c r="B63" t="n">
-        <v>93197</v>
+        <v>78993</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7951,34 +7952,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519596</v>
+        <v>519636</v>
       </c>
       <c r="R63" t="n">
-        <v>6532710</v>
+        <v>6532709</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8005,12 +8010,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8022,8 +8032,12 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AR63" t="inlineStr"/>
       <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW63" t="inlineStr">
         <is>
           <t>Viktor Säfve</t>
@@ -8037,54 +8051,54 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54013950</t>
+          <t>https://artportalen.se/Sighting/55321736</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>81095228</v>
+        <v>85451302</v>
       </c>
       <c r="B64" t="n">
-        <v>93197</v>
+        <v>96458</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>2818</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hjärtasjön med omnejd, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519615</v>
+        <v>519731</v>
       </c>
       <c r="R64" t="n">
-        <v>6532734</v>
+        <v>6532645</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8108,12 +8122,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8128,27 +8142,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81095228</t>
+          <t>https://artportalen.se/Sighting/85451302</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>54013984</v>
+        <v>85451356</v>
       </c>
       <c r="B65" t="n">
-        <v>91282</v>
+        <v>92333</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8156,37 +8170,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5685</v>
+        <v>4217</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519636</v>
+        <v>519697</v>
       </c>
       <c r="R65" t="n">
-        <v>6532709</v>
+        <v>6532776</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8210,12 +8224,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8227,76 +8241,68 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AR65" t="inlineStr"/>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54013984</t>
+          <t>https://artportalen.se/Sighting/85451356</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132028911</v>
+        <v>54013950</v>
       </c>
       <c r="B66" t="n">
-        <v>79373</v>
+        <v>93197</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bavlingeskogen, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519619</v>
+        <v>519596</v>
       </c>
       <c r="R66" t="n">
-        <v>6532722</v>
+        <v>6532710</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8320,12 +8326,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8334,34 +8340,34 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
+      <c r="AR66" t="inlineStr"/>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132028911</t>
+          <t>https://artportalen.se/Sighting/54013950</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55321959</v>
+        <v>81095228</v>
       </c>
       <c r="B67" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8369,38 +8375,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Hjärtasjön med omnejd, Nrk</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519636</v>
+        <v>519615</v>
       </c>
       <c r="R67" t="n">
-        <v>6532709</v>
+        <v>6532734</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8427,17 +8429,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8450,73 +8447,64 @@
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321959</t>
+          <t>https://artportalen.se/Sighting/81095228</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>55321978</v>
+        <v>54013984</v>
       </c>
       <c r="B68" t="n">
-        <v>79946</v>
+        <v>91282</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519596</v>
+        <v>519636</v>
       </c>
       <c r="R68" t="n">
-        <v>6532710</v>
+        <v>6532709</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8543,17 +8531,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8565,12 +8548,8 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
+      <c r="AR68" t="inlineStr"/>
       <c r="AT68" t="inlineStr"/>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW68" t="inlineStr">
         <is>
           <t>Viktor Säfve</t>
@@ -8584,58 +8563,61 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321978</t>
+          <t>https://artportalen.se/Sighting/54013984</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>55322041</v>
+        <v>132028911</v>
       </c>
       <c r="B69" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Bavlingeskogen, Nrk</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519628</v>
+        <v>519619</v>
       </c>
       <c r="R69" t="n">
-        <v>6532734</v>
+        <v>6532722</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8659,17 +8641,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Observerad av Toni Berglund</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8678,35 +8655,31 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322041</t>
+          <t>https://artportalen.se/Sighting/132028911</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>85451274</v>
+        <v>55321959</v>
       </c>
       <c r="B70" t="n">
         <v>79946</v>
@@ -8734,20 +8707,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519738</v>
+        <v>519636</v>
       </c>
       <c r="R70" t="n">
-        <v>6532781</v>
+        <v>6532709</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8771,12 +8748,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8789,29 +8771,34 @@
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451274</t>
+          <t>https://artportalen.se/Sighting/55321959</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>85451350</v>
+        <v>55321978</v>
       </c>
       <c r="B71" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8819,37 +8806,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520143</v>
+        <v>519596</v>
       </c>
       <c r="R71" t="n">
-        <v>6532731</v>
+        <v>6532710</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8873,12 +8864,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8891,26 +8887,31 @@
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451350</t>
+          <t>https://artportalen.se/Sighting/55321978</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>85451285</v>
+        <v>55322041</v>
       </c>
       <c r="B72" t="n">
         <v>79946</v>
@@ -8938,20 +8939,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520192</v>
+        <v>519628</v>
       </c>
       <c r="R72" t="n">
-        <v>6532728</v>
+        <v>6532734</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8975,12 +8980,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Observerad av Toni Berglund</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8993,26 +9003,31 @@
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451285</t>
+          <t>https://artportalen.se/Sighting/55322041</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>85451403</v>
+        <v>85451274</v>
       </c>
       <c r="B73" t="n">
         <v>79946</v>
@@ -9043,14 +9058,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>ost Bavlingssjön, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520311</v>
+        <v>519738</v>
       </c>
       <c r="R73" t="n">
-        <v>6532603</v>
+        <v>6532781</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9108,54 +9123,54 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451403</t>
+          <t>https://artportalen.se/Sighting/85451274</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>80563800</v>
+        <v>85451350</v>
       </c>
       <c r="B74" t="n">
-        <v>93193</v>
+        <v>78993</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4363</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519723</v>
+        <v>520143</v>
       </c>
       <c r="R74" t="n">
-        <v>6531341</v>
+        <v>6532731</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9179,12 +9194,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9199,27 +9214,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563800</t>
+          <t>https://artportalen.se/Sighting/85451350</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>80563801</v>
+        <v>85451285</v>
       </c>
       <c r="B75" t="n">
-        <v>93197</v>
+        <v>79946</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9227,37 +9242,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519697</v>
+        <v>520192</v>
       </c>
       <c r="R75" t="n">
-        <v>6531333</v>
+        <v>6532728</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9281,12 +9296,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9301,27 +9316,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563801</t>
+          <t>https://artportalen.se/Sighting/85451285</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>80563803</v>
+        <v>85451403</v>
       </c>
       <c r="B76" t="n">
-        <v>93197</v>
+        <v>79946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9329,37 +9344,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>ost Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519682</v>
+        <v>520311</v>
       </c>
       <c r="R76" t="n">
-        <v>6531348</v>
+        <v>6532603</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9383,12 +9398,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9403,49 +9418,49 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563803</t>
+          <t>https://artportalen.se/Sighting/85451403</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>80563804</v>
+        <v>80563800</v>
       </c>
       <c r="B77" t="n">
-        <v>93197</v>
+        <v>93193</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9455,10 +9470,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519675</v>
+        <v>519723</v>
       </c>
       <c r="R77" t="n">
-        <v>6531363</v>
+        <v>6531341</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9516,13 +9531,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563804</t>
+          <t>https://artportalen.se/Sighting/80563800</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>80563805</v>
+        <v>80563801</v>
       </c>
       <c r="B78" t="n">
         <v>93197</v>
@@ -9557,10 +9572,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519682</v>
+        <v>519697</v>
       </c>
       <c r="R78" t="n">
-        <v>6531371</v>
+        <v>6531333</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9618,51 +9633,51 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563805</t>
+          <t>https://artportalen.se/Sighting/80563801</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>54014169</v>
+        <v>80563803</v>
       </c>
       <c r="B79" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519821</v>
+        <v>519682</v>
       </c>
       <c r="R79" t="n">
-        <v>6531449</v>
+        <v>6531348</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9689,12 +9704,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9706,69 +9721,68 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AR79" t="inlineStr"/>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54014169</t>
+          <t>https://artportalen.se/Sighting/80563803</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>85451261</v>
+        <v>80563804</v>
       </c>
       <c r="B80" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519855</v>
+        <v>519675</v>
       </c>
       <c r="R80" t="n">
-        <v>6531422</v>
+        <v>6531363</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9792,12 +9806,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9812,27 +9826,27 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451261</t>
+          <t>https://artportalen.se/Sighting/80563804</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>55322013</v>
+        <v>80563805</v>
       </c>
       <c r="B81" t="n">
-        <v>79946</v>
+        <v>93197</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9840,38 +9854,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>519789</v>
+        <v>519682</v>
       </c>
       <c r="R81" t="n">
-        <v>6531472</v>
+        <v>6531371</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9898,17 +9908,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9921,69 +9926,64 @@
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322013</t>
+          <t>https://artportalen.se/Sighting/80563805</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>80563802</v>
+        <v>54014169</v>
       </c>
       <c r="B82" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>519687</v>
+        <v>519821</v>
       </c>
       <c r="R82" t="n">
-        <v>6531345</v>
+        <v>6531449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10027,57 +10027,53 @@
       <c r="AG82" t="b">
         <v>0</v>
       </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>silverstubbe</t>
-        </is>
-      </c>
+      <c r="AR82" t="inlineStr"/>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563802</t>
+          <t>https://artportalen.se/Sighting/54014169</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>85451281</v>
+        <v>85451261</v>
       </c>
       <c r="B83" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10087,10 +10083,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519882</v>
+        <v>519855</v>
       </c>
       <c r="R83" t="n">
-        <v>6531425</v>
+        <v>6531422</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10147,6 +10143,331 @@
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451261</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>55322013</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>519789</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6531472</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2011-05-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Viktor Säfve</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Viktor Säfve</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55322013</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>80563802</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>519687</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6531345</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2019-09-29</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>silverstubbe</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563802</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85451281</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>väst Bavlingssjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>519882</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6531425</v>
+      </c>
+      <c r="S86" t="n">
+        <v>25</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2020-05-03</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/85451281</t>
         </is>
@@ -10236,6 +10557,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>137166501</v>
       </c>
       <c r="B9" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136646193</v>
       </c>
       <c r="B11" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137166519</v>
       </c>
       <c r="B12" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>137168022</v>
       </c>
       <c r="B35" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>137166501</v>
       </c>
       <c r="B9" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>136646193</v>
       </c>
       <c r="B11" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137166519</v>
       </c>
       <c r="B12" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>137168022</v>
       </c>
       <c r="B35" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1986,11 +1986,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2108,11 +2104,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -3659,11 +3651,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -5947,11 +5935,7 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>137166501</v>
       </c>
       <c r="B9" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137166519</v>
       </c>
       <c r="B12" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>115377556</v>
       </c>
       <c r="B13" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>115377695</v>
       </c>
       <c r="B14" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>129810219</v>
       </c>
       <c r="B27" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>137168022</v>
       </c>
       <c r="B35" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>120635120</v>
       </c>
       <c r="B46" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>137166501</v>
       </c>
       <c r="B9" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137166519</v>
       </c>
       <c r="B12" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>137168022</v>
       </c>
       <c r="B35" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -1494,7 +1494,7 @@
         <v>137166501</v>
       </c>
       <c r="B9" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137166519</v>
       </c>
       <c r="B12" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>137168022</v>
       </c>
       <c r="B35" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
